--- a/files/港岛-北角-嘉居．天后.xlsx
+++ b/files/港岛-北角-嘉居．天后.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="嘉居．天后 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="嘉居．天后" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -145,8 +171,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,19 +219,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,13 +237,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -607,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -4098,115 +4136,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>嘉居．天后 - 嘉居．天后 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>嘉居．天后 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>74 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>72 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 946呎 (3房)
 招标单位
@@ -4214,16 +4252,16 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 857呎 (3房)
 招标单位
@@ -4231,179 +4269,179 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,368万
+$1368万
 $28,679/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
-$1,068万
+$1068万
 $29,584/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
-$1,168万
+$1168万
 $32,355/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,339万
+$1339万
 $28,067/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
-$1,048万
+$1048万
 $29,030/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
-$1,148万
+$1148万
 $31,801/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,312万
+$1312万
 $27,497/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
-$1,021万
+$1021万
 $28,277/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
-$1,165万
+$1165万
 $32,269/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,301万
+$1301万
 $27,279/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
-$1,013万
+$1013万
 $28,050/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
-$1,102万
+$1102万
 $30,521/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,348万
+$1348万
 $28,252/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
-$1,012万
+$1012万
 $28,028/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
-$1,088万
+$1088万
 $30,139/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,327万
+$1327万
 $27,822/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $997万
@@ -4411,30 +4449,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
-$1,063万
+$1063万
 $29,446/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,270万
+$1270万
 $26,623/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $989万
@@ -4442,30 +4480,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
-$1,051万
+$1051万
 $29,108/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,260万
+$1260万
 $26,419/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $981万
@@ -4473,30 +4511,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
-$1,038万
+$1038万
 $28,753/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,250万
+$1250万
 $26,212/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $973万
@@ -4504,30 +4542,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
-$1,026万
+$1026万
 $28,421/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,238万
+$1238万
 $25,950/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $966万
@@ -4535,30 +4573,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
-$1,016万
+$1016万
 $28,133/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,228万
+$1228万
 $25,748/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $958万
@@ -4566,30 +4604,30 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
-$1,006万
+$1006万
 $27,853/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,218万
+$1218万
 $25,541/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $950万
@@ -4597,7 +4635,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
 $996万
@@ -4606,21 +4644,21 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,209万
+$1209万
 $25,342/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $943万
@@ -4628,7 +4666,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
 $986万
@@ -4637,21 +4675,21 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,199万
+$1199万
 $25,143/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $935万
@@ -4659,7 +4697,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
 $976万
@@ -4668,21 +4706,21 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,190万
+$1190万
 $24,939/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $928万
@@ -4690,7 +4728,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
 $966万
@@ -4699,21 +4737,21 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,180万
+$1180万
 $24,742/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $920万
@@ -4721,7 +4759,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
 $947万
@@ -4730,21 +4768,21 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,170万
+$1170万
 $24,526/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $913万
@@ -4752,7 +4790,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
 $940万
@@ -4761,21 +4799,21 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,162万
+$1162万
 $24,356/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $906万
@@ -4783,7 +4821,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
 $932万
@@ -4792,21 +4830,21 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,150万
+$1150万
 $24,109/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $899万
@@ -4814,7 +4852,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
 $925万
@@ -4823,21 +4861,21 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,140万
+$1140万
 $23,895/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $892万
@@ -4845,7 +4883,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
 $918万
@@ -4854,21 +4892,21 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,132万
+$1132万
 $23,727/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $916万
@@ -4876,7 +4914,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
 $944万
@@ -4885,21 +4923,21 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,123万
+$1123万
 $23,539/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $878万
@@ -4907,7 +4945,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
 $903万
@@ -4916,21 +4954,21 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 477呎 (3房)
-$1,154万
+$1154万
 $24,203/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 361呎 (2房)
 $870万
@@ -4938,7 +4976,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D30" s="18" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 361呎 (2房)
 $896万
@@ -4947,32 +4985,32 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 439呎 (3房)
-$1,449万
+$1449万
 $33,002/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 324呎 (2房)
-$1,080万
+$1080万
 $33,333/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 324呎 (2房)
-$1,098万
+$1098万
 $33,889/呎
 (已售)</t>
         </is>
@@ -4980,7 +5018,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
